--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126503198</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126503200</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126503199</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126503198</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126503200</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126503199</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,4532 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127843150</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>444510</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7037554</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127843152</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>444458</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7037500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127843102</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>444566</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127843149</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>444505</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7037527</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127843141</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>444571</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7037448</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127843145</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>444478</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7037536</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål?</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127843131</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>444467</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7037464</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127843135</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>444519</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7037467</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127843156</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>444572</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7037457</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127843110</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>444513</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7037512</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127843122</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>444462</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7037557</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127843126</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>444461</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7037529</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127843146</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91334</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>444502</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7037488</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127843157</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>444826</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7037952</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127843140</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>444560</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7037432</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127843117</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>444554</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7037595</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127843099</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>444641</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7037742</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127843154</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>444480</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7037475</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127843109</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>444542</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7037666</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127843129</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>444461</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7037489</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127843133</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>444477</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7037464</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127843147</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91334</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>444554</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7037482</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127843153</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>444466</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7037481</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127843115</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>444541</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7037575</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127843120</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>444461</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7037569</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127843107</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>444567</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7037695</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127843155</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>444538</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7037421</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127843128</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>444473</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7037520</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127843148</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>444520</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7037511</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127843108</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>444547</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7037683</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127843144</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>444731</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7037835</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127843106</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>444593</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7037659</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127843103</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>444547</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7037649</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127843151</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>444480</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7037529</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127843124</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>444477</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7037536</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127843101</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>444760</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7037894</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127843139</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>444511</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7037473</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127843104</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>444764</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7037903</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127843142</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>444554</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7037489</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127843138</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>444523</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7037462</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127843111</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>444514</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7037529</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127843105</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>444698</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7037783</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127843143</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>444720</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7037681</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127843113</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>444529</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7037528</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127843112</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hällberget  V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>444532</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7037525</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126503198</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126503200</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126503199</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127843150</v>
       </c>
       <c r="B5" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127843152</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B7" t="n">
-        <v>92035</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R7" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B8" t="n">
-        <v>91356</v>
+        <v>92038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R8" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>127843141</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127843145</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127843131</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127843135</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127843156</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127843110</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127843122</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127843126</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91334</v>
+        <v>91359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R17" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B18" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R18" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2377,7 @@
         <v>127843140</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127843117</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843099</v>
+        <v>127843109</v>
       </c>
       <c r="B21" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444641</v>
+        <v>444542</v>
       </c>
       <c r="R21" t="n">
-        <v>7037742</v>
+        <v>7037666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2649,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2678,7 +2683,7 @@
         <v>127843154</v>
       </c>
       <c r="B22" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843109</v>
+        <v>127843099</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>91341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2788,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444542</v>
+        <v>444641</v>
       </c>
       <c r="R23" t="n">
-        <v>7037666</v>
+        <v>7037742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,7 +2877,7 @@
         <v>127843129</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>127843133</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>127843147</v>
       </c>
       <c r="B26" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>127843153</v>
       </c>
       <c r="B27" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>127843115</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>127843120</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>127843107</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>127843128</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843148</v>
+        <v>127843144</v>
       </c>
       <c r="B33" t="n">
-        <v>91356</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,34 +3788,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444520</v>
+        <v>444731</v>
       </c>
       <c r="R33" t="n">
-        <v>7037511</v>
+        <v>7037835</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3874,10 +3882,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>91359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,21 +3893,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3917,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R34" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,11 +3953,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3976,10 +3979,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843144</v>
+        <v>127843108</v>
       </c>
       <c r="B35" t="n">
-        <v>57823</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,42 +3990,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444731</v>
+        <v>444547</v>
       </c>
       <c r="R35" t="n">
-        <v>7037835</v>
+        <v>7037683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4050,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4084,7 +4084,7 @@
         <v>127843106</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127843103</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>127843151</v>
       </c>
       <c r="B38" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>127843124</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>127843101</v>
       </c>
       <c r="B40" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>127843139</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>127843104</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>127843142</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127843138</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>127843111</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>127843105</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127843143</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>127843113</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>127843112</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126503198</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126503200</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126503199</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127843150</v>
       </c>
       <c r="B5" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127843152</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B7" t="n">
-        <v>91359</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R7" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B8" t="n">
-        <v>92038</v>
+        <v>91367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R8" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>127843141</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127843145</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127843131</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127843135</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127843156</v>
       </c>
       <c r="B13" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127843110</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127843122</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>127843126</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B17" t="n">
-        <v>91359</v>
+        <v>91345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R17" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843146</v>
+        <v>127843140</v>
       </c>
       <c r="B18" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444502</v>
+        <v>444560</v>
       </c>
       <c r="R18" t="n">
-        <v>7037488</v>
+        <v>7037432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843140</v>
+        <v>127843117</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444560</v>
+        <v>444554</v>
       </c>
       <c r="R19" t="n">
-        <v>7037432</v>
+        <v>7037595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843117</v>
+        <v>127843157</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444554</v>
+        <v>444826</v>
       </c>
       <c r="R20" t="n">
-        <v>7037595</v>
+        <v>7037952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843109</v>
+        <v>127843099</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444542</v>
+        <v>444641</v>
       </c>
       <c r="R21" t="n">
-        <v>7037666</v>
+        <v>7037742</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2683,7 +2678,7 @@
         <v>127843154</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843099</v>
+        <v>127843109</v>
       </c>
       <c r="B23" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2783,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444641</v>
+        <v>444542</v>
       </c>
       <c r="R23" t="n">
-        <v>7037742</v>
+        <v>7037666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843129</v>
+        <v>127843147</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>91345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444461</v>
+        <v>444554</v>
       </c>
       <c r="R24" t="n">
-        <v>7037489</v>
+        <v>7037482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2945,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843133</v>
+        <v>127843129</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444477</v>
+        <v>444461</v>
       </c>
       <c r="R25" t="n">
-        <v>7037464</v>
+        <v>7037489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843147</v>
+        <v>127843133</v>
       </c>
       <c r="B26" t="n">
-        <v>91337</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444554</v>
+        <v>444477</v>
       </c>
       <c r="R26" t="n">
-        <v>7037482</v>
+        <v>7037464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3178,7 +3178,7 @@
         <v>127843153</v>
       </c>
       <c r="B27" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>127843115</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>127843120</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>127843107</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>127843128</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843144</v>
+        <v>127843148</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>91367</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,42 +3788,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444731</v>
+        <v>444520</v>
       </c>
       <c r="R33" t="n">
-        <v>7037835</v>
+        <v>7037511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3882,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843148</v>
+        <v>127843108</v>
       </c>
       <c r="B34" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3893,21 +3885,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3917,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444520</v>
+        <v>444547</v>
       </c>
       <c r="R34" t="n">
-        <v>7037511</v>
+        <v>7037683</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,6 +3945,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3979,10 +3976,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843108</v>
+        <v>127843144</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57832</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,34 +3987,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444547</v>
+        <v>444731</v>
       </c>
       <c r="R35" t="n">
-        <v>7037683</v>
+        <v>7037835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4084,7 +4084,7 @@
         <v>127843106</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127843103</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>127843151</v>
       </c>
       <c r="B38" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>127843124</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,32 +4492,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843101</v>
+        <v>127843139</v>
       </c>
       <c r="B40" t="n">
-        <v>92038</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444760</v>
+        <v>444511</v>
       </c>
       <c r="R40" t="n">
-        <v>7037894</v>
+        <v>7037473</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,6 +4563,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4589,32 +4594,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843139</v>
+        <v>127843101</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>92046</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4624,10 +4629,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444511</v>
+        <v>444760</v>
       </c>
       <c r="R41" t="n">
-        <v>7037473</v>
+        <v>7037894</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,11 +4665,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4694,7 +4694,7 @@
         <v>127843104</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>127843142</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127843138</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>127843111</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>127843105</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127843143</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>127843113</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>127843112</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>127843150</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127843152</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127843102</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127843149</v>
       </c>
       <c r="B8" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127843156</v>
       </c>
       <c r="B13" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91345</v>
+        <v>91368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R17" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B20" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R20" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
         <v>127843099</v>
       </c>
       <c r="B21" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>127843154</v>
       </c>
       <c r="B22" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843147</v>
+        <v>127843129</v>
       </c>
       <c r="B24" t="n">
-        <v>91345</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444554</v>
+        <v>444461</v>
       </c>
       <c r="R24" t="n">
-        <v>7037482</v>
+        <v>7037489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,6 +2945,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843129</v>
+        <v>127843133</v>
       </c>
       <c r="B25" t="n">
         <v>57672</v>
@@ -3006,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444461</v>
+        <v>444477</v>
       </c>
       <c r="R25" t="n">
-        <v>7037489</v>
+        <v>7037464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843133</v>
+        <v>127843147</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>91346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444477</v>
+        <v>444554</v>
       </c>
       <c r="R26" t="n">
-        <v>7037464</v>
+        <v>7037482</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,11 +3149,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3178,7 +3178,7 @@
         <v>127843153</v>
       </c>
       <c r="B27" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127843148</v>
       </c>
       <c r="B33" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>127843151</v>
       </c>
       <c r="B38" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,32 +4492,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843139</v>
+        <v>127843101</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>92047</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444511</v>
+        <v>444760</v>
       </c>
       <c r="R40" t="n">
-        <v>7037473</v>
+        <v>7037894</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,11 +4563,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,32 +4589,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843101</v>
+        <v>127843139</v>
       </c>
       <c r="B41" t="n">
-        <v>92046</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4629,10 +4624,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444760</v>
+        <v>444511</v>
       </c>
       <c r="R41" t="n">
-        <v>7037894</v>
+        <v>7037473</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4660,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843102</v>
+        <v>127843141</v>
       </c>
       <c r="B7" t="n">
-        <v>92047</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444566</v>
+        <v>444571</v>
       </c>
       <c r="R7" t="n">
-        <v>7037573</v>
+        <v>7037448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843149</v>
+        <v>127843145</v>
       </c>
       <c r="B8" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444505</v>
+        <v>444478</v>
       </c>
       <c r="R8" t="n">
-        <v>7037527</v>
+        <v>7037536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843141</v>
+        <v>127843102</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>92047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444571</v>
+        <v>444566</v>
       </c>
       <c r="R9" t="n">
-        <v>7037448</v>
+        <v>7037573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843145</v>
+        <v>127843149</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444478</v>
+        <v>444505</v>
       </c>
       <c r="R10" t="n">
-        <v>7037536</v>
+        <v>7037527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B17" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R17" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B20" t="n">
-        <v>91346</v>
+        <v>91368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R20" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843099</v>
+        <v>127843109</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444641</v>
+        <v>444542</v>
       </c>
       <c r="R21" t="n">
-        <v>7037742</v>
+        <v>7037666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2649,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843109</v>
+        <v>127843099</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2788,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444542</v>
+        <v>444641</v>
       </c>
       <c r="R23" t="n">
-        <v>7037666</v>
+        <v>7037742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B31" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R31" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,10 +3680,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3691,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R32" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,11 +3751,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843148</v>
+        <v>127843108</v>
       </c>
       <c r="B33" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444520</v>
+        <v>444547</v>
       </c>
       <c r="R33" t="n">
-        <v>7037511</v>
+        <v>7037683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,6 +3848,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,10 +3879,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,21 +3890,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R34" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,11 +3950,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4293,10 +4293,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127843151</v>
+        <v>127843124</v>
       </c>
       <c r="B38" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444480</v>
+        <v>444477</v>
       </c>
       <c r="R38" t="n">
-        <v>7037529</v>
+        <v>7037536</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4364,6 +4364,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4390,10 +4395,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127843124</v>
+        <v>127843151</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4401,21 +4406,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4425,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444477</v>
+        <v>444480</v>
       </c>
       <c r="R39" t="n">
-        <v>7037536</v>
+        <v>7037529</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,11 +4466,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4492,32 +4492,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843101</v>
+        <v>127843139</v>
       </c>
       <c r="B40" t="n">
-        <v>92047</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444760</v>
+        <v>444511</v>
       </c>
       <c r="R40" t="n">
-        <v>7037894</v>
+        <v>7037473</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,6 +4563,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4589,32 +4594,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843139</v>
+        <v>127843101</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>92047</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4624,10 +4629,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444511</v>
+        <v>444760</v>
       </c>
       <c r="R41" t="n">
-        <v>7037473</v>
+        <v>7037894</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,11 +4665,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>127843150</v>
       </c>
       <c r="B5" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127843152</v>
       </c>
       <c r="B6" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843141</v>
+        <v>127843102</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>92048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444571</v>
+        <v>444566</v>
       </c>
       <c r="R7" t="n">
-        <v>7037448</v>
+        <v>7037573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843145</v>
+        <v>127843141</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444478</v>
+        <v>444571</v>
       </c>
       <c r="R8" t="n">
-        <v>7037536</v>
+        <v>7037448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påbörjat bohål?</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843102</v>
+        <v>127843145</v>
       </c>
       <c r="B9" t="n">
-        <v>92047</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444566</v>
+        <v>444478</v>
       </c>
       <c r="R9" t="n">
-        <v>7037573</v>
+        <v>7037536</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,7 +1479,7 @@
         <v>127843149</v>
       </c>
       <c r="B10" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127843156</v>
       </c>
       <c r="B13" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>127843146</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127843157</v>
       </c>
       <c r="B20" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843109</v>
+        <v>127843099</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444542</v>
+        <v>444641</v>
       </c>
       <c r="R21" t="n">
-        <v>7037666</v>
+        <v>7037742</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2683,7 +2678,7 @@
         <v>127843154</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843099</v>
+        <v>127843109</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2783,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444641</v>
+        <v>444542</v>
       </c>
       <c r="R23" t="n">
-        <v>7037742</v>
+        <v>7037666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843129</v>
+        <v>127843147</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444461</v>
+        <v>444554</v>
       </c>
       <c r="R24" t="n">
-        <v>7037489</v>
+        <v>7037482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2945,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,7 +2971,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843133</v>
+        <v>127843129</v>
       </c>
       <c r="B25" t="n">
         <v>57672</v>
@@ -3011,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444477</v>
+        <v>444461</v>
       </c>
       <c r="R25" t="n">
-        <v>7037464</v>
+        <v>7037489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843147</v>
+        <v>127843133</v>
       </c>
       <c r="B26" t="n">
-        <v>91346</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444554</v>
+        <v>444477</v>
       </c>
       <c r="R26" t="n">
-        <v>7037482</v>
+        <v>7037464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3178,7 +3178,7 @@
         <v>127843153</v>
       </c>
       <c r="B27" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127843155</v>
       </c>
       <c r="B32" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>127843148</v>
       </c>
       <c r="B34" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>127843151</v>
       </c>
       <c r="B39" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,32 +4492,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843139</v>
+        <v>127843101</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>92048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444511</v>
+        <v>444760</v>
       </c>
       <c r="R40" t="n">
-        <v>7037473</v>
+        <v>7037894</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,11 +4563,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,32 +4589,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843101</v>
+        <v>127843139</v>
       </c>
       <c r="B41" t="n">
-        <v>92047</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4629,10 +4624,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444760</v>
+        <v>444511</v>
       </c>
       <c r="R41" t="n">
-        <v>7037894</v>
+        <v>7037473</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4660,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>127843150</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127843152</v>
       </c>
       <c r="B6" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127843102</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843141</v>
+        <v>127843149</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444571</v>
+        <v>444505</v>
       </c>
       <c r="R8" t="n">
-        <v>7037448</v>
+        <v>7037527</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1369,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843145</v>
+        <v>127843141</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1409,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444478</v>
+        <v>444571</v>
       </c>
       <c r="R9" t="n">
-        <v>7037536</v>
+        <v>7037448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1444,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påbörjat bohål?</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843149</v>
+        <v>127843145</v>
       </c>
       <c r="B10" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444505</v>
+        <v>444478</v>
       </c>
       <c r="R10" t="n">
-        <v>7037527</v>
+        <v>7037536</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,7 +1780,7 @@
         <v>127843156</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843110</v>
+        <v>127843126</v>
       </c>
       <c r="B14" t="n">
         <v>57672</v>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444513</v>
+        <v>444461</v>
       </c>
       <c r="R14" t="n">
-        <v>7037512</v>
+        <v>7037529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843122</v>
+        <v>127843110</v>
       </c>
       <c r="B15" t="n">
         <v>57672</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444462</v>
+        <v>444513</v>
       </c>
       <c r="R15" t="n">
-        <v>7037557</v>
+        <v>7037512</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843126</v>
+        <v>127843122</v>
       </c>
       <c r="B16" t="n">
         <v>57672</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444461</v>
+        <v>444462</v>
       </c>
       <c r="R16" t="n">
-        <v>7037529</v>
+        <v>7037557</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91347</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R17" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B20" t="n">
-        <v>91369</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R20" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
         <v>127843099</v>
       </c>
       <c r="B21" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>127843154</v>
       </c>
       <c r="B22" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843147</v>
+        <v>127843129</v>
       </c>
       <c r="B24" t="n">
-        <v>91347</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444554</v>
+        <v>444461</v>
       </c>
       <c r="R24" t="n">
-        <v>7037482</v>
+        <v>7037489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,6 +2945,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843129</v>
+        <v>127843133</v>
       </c>
       <c r="B25" t="n">
         <v>57672</v>
@@ -3006,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444461</v>
+        <v>444477</v>
       </c>
       <c r="R25" t="n">
-        <v>7037489</v>
+        <v>7037464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843133</v>
+        <v>127843147</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444477</v>
+        <v>444554</v>
       </c>
       <c r="R26" t="n">
-        <v>7037464</v>
+        <v>7037482</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,11 +3149,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3178,7 +3178,7 @@
         <v>127843153</v>
       </c>
       <c r="B27" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R31" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B32" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R32" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,6 +3746,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843108</v>
+        <v>127843144</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,34 +3788,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444547</v>
+        <v>444731</v>
       </c>
       <c r="R33" t="n">
-        <v>7037683</v>
+        <v>7037835</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,11 +3856,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3882,7 +3885,7 @@
         <v>127843148</v>
       </c>
       <c r="B34" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,10 +3979,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843144</v>
+        <v>127843108</v>
       </c>
       <c r="B35" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,42 +3990,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444731</v>
+        <v>444547</v>
       </c>
       <c r="R35" t="n">
-        <v>7037835</v>
+        <v>7037683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4050,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,10 +4293,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127843124</v>
+        <v>127843151</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444477</v>
+        <v>444480</v>
       </c>
       <c r="R38" t="n">
-        <v>7037536</v>
+        <v>7037529</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4364,11 +4364,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4395,10 +4390,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127843151</v>
+        <v>127843124</v>
       </c>
       <c r="B39" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4406,21 +4401,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4430,10 +4425,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444480</v>
+        <v>444477</v>
       </c>
       <c r="R39" t="n">
-        <v>7037529</v>
+        <v>7037536</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,6 +4461,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4495,7 +4495,7 @@
         <v>127843101</v>
       </c>
       <c r="B40" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127843104</v>
+        <v>127843142</v>
       </c>
       <c r="B42" t="n">
         <v>57672</v>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444764</v>
+        <v>444554</v>
       </c>
       <c r="R42" t="n">
-        <v>7037903</v>
+        <v>7037489</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4793,7 +4793,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127843142</v>
+        <v>127843104</v>
       </c>
       <c r="B43" t="n">
         <v>57672</v>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444554</v>
+        <v>444764</v>
       </c>
       <c r="R43" t="n">
-        <v>7037489</v>
+        <v>7037903</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5099,7 +5099,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127843105</v>
+        <v>127843143</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444698</v>
+        <v>444720</v>
       </c>
       <c r="R46" t="n">
-        <v>7037783</v>
+        <v>7037681</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,7 +5201,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127843143</v>
+        <v>127843105</v>
       </c>
       <c r="B47" t="n">
         <v>57672</v>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444720</v>
+        <v>444698</v>
       </c>
       <c r="R47" t="n">
-        <v>7037681</v>
+        <v>7037783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843141</v>
+        <v>127843145</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444571</v>
+        <v>444478</v>
       </c>
       <c r="R9" t="n">
-        <v>7037448</v>
+        <v>7037536</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843145</v>
+        <v>127843141</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444478</v>
+        <v>444571</v>
       </c>
       <c r="R10" t="n">
-        <v>7037536</v>
+        <v>7037448</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påbörjat bohål?</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843110</v>
+        <v>127843122</v>
       </c>
       <c r="B15" t="n">
         <v>57672</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444513</v>
+        <v>444462</v>
       </c>
       <c r="R15" t="n">
-        <v>7037512</v>
+        <v>7037557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843122</v>
+        <v>127843110</v>
       </c>
       <c r="B16" t="n">
         <v>57672</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444462</v>
+        <v>444513</v>
       </c>
       <c r="R16" t="n">
-        <v>7037557</v>
+        <v>7037512</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843140</v>
+        <v>127843117</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444560</v>
+        <v>444554</v>
       </c>
       <c r="R18" t="n">
-        <v>7037432</v>
+        <v>7037595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843117</v>
+        <v>127843140</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444554</v>
+        <v>444560</v>
       </c>
       <c r="R19" t="n">
-        <v>7037595</v>
+        <v>7037432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843129</v>
+        <v>127843147</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444461</v>
+        <v>444554</v>
       </c>
       <c r="R24" t="n">
-        <v>7037489</v>
+        <v>7037482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2945,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843147</v>
+        <v>127843129</v>
       </c>
       <c r="B26" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444554</v>
+        <v>444461</v>
       </c>
       <c r="R26" t="n">
-        <v>7037482</v>
+        <v>7037489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R31" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,10 +3680,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3691,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R32" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,11 +3751,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843144</v>
+        <v>127843148</v>
       </c>
       <c r="B33" t="n">
-        <v>57832</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,42 +3788,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444731</v>
+        <v>444520</v>
       </c>
       <c r="R33" t="n">
-        <v>7037835</v>
+        <v>7037511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3882,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843148</v>
+        <v>127843144</v>
       </c>
       <c r="B34" t="n">
-        <v>91370</v>
+        <v>57832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3893,34 +3885,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444520</v>
+        <v>444731</v>
       </c>
       <c r="R34" t="n">
-        <v>7037511</v>
+        <v>7037835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843106</v>
+        <v>127843103</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4110,16 +4110,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444593</v>
+        <v>444547</v>
       </c>
       <c r="R36" t="n">
-        <v>7037659</v>
+        <v>7037649</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4156,7 +4164,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,7 +4191,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127843103</v>
+        <v>127843106</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4212,24 +4220,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444547</v>
+        <v>444593</v>
       </c>
       <c r="R37" t="n">
-        <v>7037649</v>
+        <v>7037659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4691,7 +4691,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127843142</v>
+        <v>127843104</v>
       </c>
       <c r="B42" t="n">
         <v>57672</v>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444554</v>
+        <v>444764</v>
       </c>
       <c r="R42" t="n">
-        <v>7037489</v>
+        <v>7037903</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4793,7 +4793,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127843104</v>
+        <v>127843142</v>
       </c>
       <c r="B43" t="n">
         <v>57672</v>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444764</v>
+        <v>444554</v>
       </c>
       <c r="R43" t="n">
-        <v>7037903</v>
+        <v>7037489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127843138</v>
+        <v>127843111</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444523</v>
+        <v>444514</v>
       </c>
       <c r="R44" t="n">
-        <v>7037462</v>
+        <v>7037529</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4997,7 +4997,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127843111</v>
+        <v>127843138</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444514</v>
+        <v>444523</v>
       </c>
       <c r="R45" t="n">
-        <v>7037529</v>
+        <v>7037462</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5099,7 +5099,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127843143</v>
+        <v>127843105</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444720</v>
+        <v>444698</v>
       </c>
       <c r="R46" t="n">
-        <v>7037681</v>
+        <v>7037783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,7 +5201,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127843105</v>
+        <v>127843143</v>
       </c>
       <c r="B47" t="n">
         <v>57672</v>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444698</v>
+        <v>444720</v>
       </c>
       <c r="R47" t="n">
-        <v>7037783</v>
+        <v>7037681</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R17" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843117</v>
+        <v>127843157</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444554</v>
+        <v>444826</v>
       </c>
       <c r="R18" t="n">
-        <v>7037595</v>
+        <v>7037952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2348,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2374,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843140</v>
+        <v>127843117</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2414,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444560</v>
+        <v>444554</v>
       </c>
       <c r="R19" t="n">
-        <v>7037432</v>
+        <v>7037595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2449,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843146</v>
+        <v>127843140</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444502</v>
+        <v>444560</v>
       </c>
       <c r="R20" t="n">
-        <v>7037488</v>
+        <v>7037432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R31" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R32" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,6 +3746,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843148</v>
+        <v>127843108</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444520</v>
+        <v>444547</v>
       </c>
       <c r="R33" t="n">
-        <v>7037511</v>
+        <v>7037683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,6 +3848,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3979,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,21 +3995,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4014,10 +4019,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R35" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B7" t="n">
-        <v>92049</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R7" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>92049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R8" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R33" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,11 +3848,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3984,10 +3979,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843148</v>
+        <v>127843108</v>
       </c>
       <c r="B35" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,21 +3990,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4019,10 +4014,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444520</v>
+        <v>444547</v>
       </c>
       <c r="R35" t="n">
-        <v>7037511</v>
+        <v>7037683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4050,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>92049</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R7" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B8" t="n">
-        <v>92049</v>
+        <v>91370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R8" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R17" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843157</v>
+        <v>127843117</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444826</v>
+        <v>444554</v>
       </c>
       <c r="R18" t="n">
-        <v>7037952</v>
+        <v>7037595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843117</v>
+        <v>127843140</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444554</v>
+        <v>444560</v>
       </c>
       <c r="R19" t="n">
-        <v>7037595</v>
+        <v>7037432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843140</v>
+        <v>127843146</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444560</v>
+        <v>444502</v>
       </c>
       <c r="R20" t="n">
-        <v>7037432</v>
+        <v>7037488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R31" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,10 +3680,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3691,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R32" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,11 +3751,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B7" t="n">
-        <v>92049</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R7" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>92049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R8" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R31" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R32" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,6 +3746,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>92049</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R7" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B8" t="n">
-        <v>92049</v>
+        <v>91370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R8" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R17" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843117</v>
+        <v>127843157</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444554</v>
+        <v>444826</v>
       </c>
       <c r="R18" t="n">
-        <v>7037595</v>
+        <v>7037952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2348,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2374,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843140</v>
+        <v>127843117</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2414,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444560</v>
+        <v>444554</v>
       </c>
       <c r="R19" t="n">
-        <v>7037432</v>
+        <v>7037595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2449,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843146</v>
+        <v>127843140</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444502</v>
+        <v>444560</v>
       </c>
       <c r="R20" t="n">
-        <v>7037488</v>
+        <v>7037432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R31" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,10 +3680,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3691,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R32" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,11 +3751,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843148</v>
+        <v>127843108</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444520</v>
+        <v>444547</v>
       </c>
       <c r="R33" t="n">
-        <v>7037511</v>
+        <v>7037683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,6 +3848,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3979,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,21 +3995,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4014,10 +4019,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R35" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B7" t="n">
-        <v>92049</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R7" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B8" t="n">
-        <v>91370</v>
+        <v>92049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R8" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R17" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843157</v>
+        <v>127843117</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444826</v>
+        <v>444554</v>
       </c>
       <c r="R18" t="n">
-        <v>7037952</v>
+        <v>7037595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843117</v>
+        <v>127843140</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444554</v>
+        <v>444560</v>
       </c>
       <c r="R19" t="n">
-        <v>7037595</v>
+        <v>7037432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843140</v>
+        <v>127843146</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444560</v>
+        <v>444502</v>
       </c>
       <c r="R20" t="n">
-        <v>7037432</v>
+        <v>7037488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R33" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,11 +3848,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3984,10 +3979,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843148</v>
+        <v>127843108</v>
       </c>
       <c r="B35" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,21 +3990,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4019,10 +4014,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444520</v>
+        <v>444547</v>
       </c>
       <c r="R35" t="n">
-        <v>7037511</v>
+        <v>7037683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4050,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>127843150</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127843152</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843149</v>
+        <v>127843141</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444505</v>
+        <v>444571</v>
       </c>
       <c r="R7" t="n">
-        <v>7037527</v>
+        <v>7037448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843102</v>
+        <v>127843145</v>
       </c>
       <c r="B8" t="n">
-        <v>92049</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444566</v>
+        <v>444478</v>
       </c>
       <c r="R8" t="n">
-        <v>7037573</v>
+        <v>7037536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843145</v>
+        <v>127843102</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>92057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444478</v>
+        <v>444566</v>
       </c>
       <c r="R9" t="n">
-        <v>7037536</v>
+        <v>7037573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843141</v>
+        <v>127843149</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444571</v>
+        <v>444505</v>
       </c>
       <c r="R10" t="n">
-        <v>7037448</v>
+        <v>7037527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,7 +1576,7 @@
         <v>127843131</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127843135</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127843156</v>
       </c>
       <c r="B13" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843126</v>
+        <v>127843110</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444461</v>
+        <v>444513</v>
       </c>
       <c r="R14" t="n">
-        <v>7037529</v>
+        <v>7037512</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1979,7 +1979,7 @@
         <v>127843122</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843110</v>
+        <v>127843126</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444513</v>
+        <v>444461</v>
       </c>
       <c r="R16" t="n">
-        <v>7037512</v>
+        <v>7037529</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2183,7 +2183,7 @@
         <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843117</v>
+        <v>127843146</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444554</v>
+        <v>444502</v>
       </c>
       <c r="R18" t="n">
-        <v>7037595</v>
+        <v>7037488</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2348,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,7 +2377,7 @@
         <v>127843140</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843146</v>
+        <v>127843117</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57673</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444502</v>
+        <v>444554</v>
       </c>
       <c r="R20" t="n">
-        <v>7037488</v>
+        <v>7037595</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843099</v>
+        <v>127843154</v>
       </c>
       <c r="B21" t="n">
-        <v>91352</v>
+        <v>91378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444641</v>
+        <v>444480</v>
       </c>
       <c r="R21" t="n">
-        <v>7037742</v>
+        <v>7037475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127843154</v>
+        <v>127843099</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>91360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444480</v>
+        <v>444641</v>
       </c>
       <c r="R22" t="n">
-        <v>7037475</v>
+        <v>7037742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,7 +2775,7 @@
         <v>127843109</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>127843147</v>
       </c>
       <c r="B24" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843133</v>
+        <v>127843129</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444477</v>
+        <v>444461</v>
       </c>
       <c r="R25" t="n">
-        <v>7037464</v>
+        <v>7037489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843129</v>
+        <v>127843133</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444461</v>
+        <v>444477</v>
       </c>
       <c r="R26" t="n">
-        <v>7037489</v>
+        <v>7037464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127843153</v>
+        <v>127843115</v>
       </c>
       <c r="B27" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444466</v>
+        <v>444541</v>
       </c>
       <c r="R27" t="n">
-        <v>7037481</v>
+        <v>7037575</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3246,6 +3246,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843115</v>
+        <v>127843153</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3288,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444541</v>
+        <v>444466</v>
       </c>
       <c r="R28" t="n">
-        <v>7037575</v>
+        <v>7037481</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3343,11 +3348,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,7 +3377,7 @@
         <v>127843120</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>127843107</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>127843128</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>127843155</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>127843148</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843144</v>
+        <v>127843108</v>
       </c>
       <c r="B34" t="n">
-        <v>57832</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,42 +3885,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444731</v>
+        <v>444547</v>
       </c>
       <c r="R34" t="n">
-        <v>7037835</v>
+        <v>7037683</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,6 +3945,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3979,10 +3976,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843108</v>
+        <v>127843144</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>57833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,34 +3987,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444547</v>
+        <v>444731</v>
       </c>
       <c r="R35" t="n">
-        <v>7037683</v>
+        <v>7037835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843103</v>
+        <v>127843106</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4110,24 +4110,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444547</v>
+        <v>444593</v>
       </c>
       <c r="R36" t="n">
-        <v>7037649</v>
+        <v>7037659</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4164,7 +4156,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4191,10 +4183,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127843106</v>
+        <v>127843103</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,16 +4212,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444593</v>
+        <v>444547</v>
       </c>
       <c r="R37" t="n">
-        <v>7037659</v>
+        <v>7037649</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4293,10 +4293,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127843151</v>
+        <v>127843124</v>
       </c>
       <c r="B38" t="n">
-        <v>91370</v>
+        <v>57673</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444480</v>
+        <v>444477</v>
       </c>
       <c r="R38" t="n">
-        <v>7037529</v>
+        <v>7037536</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4364,6 +4364,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4390,10 +4395,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127843124</v>
+        <v>127843151</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4401,21 +4406,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4425,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444477</v>
+        <v>444480</v>
       </c>
       <c r="R39" t="n">
-        <v>7037536</v>
+        <v>7037529</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,11 +4466,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4492,32 +4492,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843101</v>
+        <v>127843139</v>
       </c>
       <c r="B40" t="n">
-        <v>92049</v>
+        <v>57673</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444760</v>
+        <v>444511</v>
       </c>
       <c r="R40" t="n">
-        <v>7037894</v>
+        <v>7037473</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,6 +4563,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4589,32 +4594,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843139</v>
+        <v>127843101</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>92057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4624,10 +4629,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444511</v>
+        <v>444760</v>
       </c>
       <c r="R41" t="n">
-        <v>7037473</v>
+        <v>7037894</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,11 +4665,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4694,7 +4694,7 @@
         <v>127843104</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>127843142</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127843111</v>
+        <v>127843138</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444514</v>
+        <v>444523</v>
       </c>
       <c r="R44" t="n">
-        <v>7037529</v>
+        <v>7037462</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4997,10 +4997,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127843138</v>
+        <v>127843111</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444523</v>
+        <v>444514</v>
       </c>
       <c r="R45" t="n">
-        <v>7037462</v>
+        <v>7037529</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5102,7 +5102,7 @@
         <v>127843105</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127843143</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>127843113</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>127843112</v>
       </c>
       <c r="B49" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843146</v>
+        <v>127843140</v>
       </c>
       <c r="B18" t="n">
-        <v>91356</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444502</v>
+        <v>444560</v>
       </c>
       <c r="R18" t="n">
-        <v>7037488</v>
+        <v>7037432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843140</v>
+        <v>127843117</v>
       </c>
       <c r="B19" t="n">
         <v>57673</v>
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444560</v>
+        <v>444554</v>
       </c>
       <c r="R19" t="n">
-        <v>7037432</v>
+        <v>7037595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843117</v>
+        <v>127843146</v>
       </c>
       <c r="B20" t="n">
-        <v>57673</v>
+        <v>91356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2511,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444554</v>
+        <v>444502</v>
       </c>
       <c r="R20" t="n">
-        <v>7037595</v>
+        <v>7037488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843154</v>
+        <v>127843109</v>
       </c>
       <c r="B21" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444480</v>
+        <v>444542</v>
       </c>
       <c r="R21" t="n">
-        <v>7037475</v>
+        <v>7037666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2649,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2680,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127843099</v>
+        <v>127843154</v>
       </c>
       <c r="B22" t="n">
-        <v>91360</v>
+        <v>91378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2691,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444641</v>
+        <v>444480</v>
       </c>
       <c r="R22" t="n">
-        <v>7037742</v>
+        <v>7037475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843109</v>
+        <v>127843099</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>91360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2788,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444542</v>
+        <v>444641</v>
       </c>
       <c r="R23" t="n">
-        <v>7037666</v>
+        <v>7037742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>91378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R31" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B32" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R32" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,6 +3746,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4492,32 +4492,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843139</v>
+        <v>127843101</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>92057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444511</v>
+        <v>444760</v>
       </c>
       <c r="R40" t="n">
-        <v>7037473</v>
+        <v>7037894</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,11 +4563,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,32 +4589,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843101</v>
+        <v>127843139</v>
       </c>
       <c r="B41" t="n">
-        <v>92057</v>
+        <v>57673</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4629,10 +4624,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444760</v>
+        <v>444511</v>
       </c>
       <c r="R41" t="n">
-        <v>7037894</v>
+        <v>7037473</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4660,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>127843150</v>
       </c>
       <c r="B5" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>127843152</v>
       </c>
       <c r="B6" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843141</v>
+        <v>127843149</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444571</v>
+        <v>444505</v>
       </c>
       <c r="R7" t="n">
-        <v>7037448</v>
+        <v>7037527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843145</v>
+        <v>127843102</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>92149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444478</v>
+        <v>444566</v>
       </c>
       <c r="R8" t="n">
-        <v>7037536</v>
+        <v>7037573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843102</v>
+        <v>127843141</v>
       </c>
       <c r="B9" t="n">
-        <v>92057</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444566</v>
+        <v>444571</v>
       </c>
       <c r="R9" t="n">
-        <v>7037573</v>
+        <v>7037448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843149</v>
+        <v>127843145</v>
       </c>
       <c r="B10" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444505</v>
+        <v>444478</v>
       </c>
       <c r="R10" t="n">
-        <v>7037527</v>
+        <v>7037536</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,7 +1576,7 @@
         <v>127843131</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>127843135</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127843156</v>
       </c>
       <c r="B13" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843110</v>
+        <v>127843126</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444513</v>
+        <v>444461</v>
       </c>
       <c r="R14" t="n">
-        <v>7037512</v>
+        <v>7037529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843122</v>
+        <v>127843110</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444462</v>
+        <v>444513</v>
       </c>
       <c r="R15" t="n">
-        <v>7037557</v>
+        <v>7037512</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843126</v>
+        <v>127843122</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444461</v>
+        <v>444462</v>
       </c>
       <c r="R16" t="n">
-        <v>7037529</v>
+        <v>7037557</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
         <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843140</v>
+        <v>127843146</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>91448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444560</v>
+        <v>444502</v>
       </c>
       <c r="R18" t="n">
-        <v>7037432</v>
+        <v>7037488</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2348,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,7 +2377,7 @@
         <v>127843117</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843146</v>
+        <v>127843140</v>
       </c>
       <c r="B20" t="n">
-        <v>91356</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444502</v>
+        <v>444560</v>
       </c>
       <c r="R20" t="n">
-        <v>7037488</v>
+        <v>7037432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843109</v>
+        <v>127843154</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444542</v>
+        <v>444480</v>
       </c>
       <c r="R21" t="n">
-        <v>7037666</v>
+        <v>7037475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2680,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127843154</v>
+        <v>127843099</v>
       </c>
       <c r="B22" t="n">
-        <v>91378</v>
+        <v>91452</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444480</v>
+        <v>444641</v>
       </c>
       <c r="R22" t="n">
-        <v>7037475</v>
+        <v>7037742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843099</v>
+        <v>127843109</v>
       </c>
       <c r="B23" t="n">
-        <v>91360</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2783,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444641</v>
+        <v>444542</v>
       </c>
       <c r="R23" t="n">
-        <v>7037742</v>
+        <v>7037666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843147</v>
+        <v>127843129</v>
       </c>
       <c r="B24" t="n">
-        <v>91356</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444554</v>
+        <v>444461</v>
       </c>
       <c r="R24" t="n">
-        <v>7037482</v>
+        <v>7037489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,6 +2945,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843129</v>
+        <v>127843133</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444461</v>
+        <v>444477</v>
       </c>
       <c r="R25" t="n">
-        <v>7037489</v>
+        <v>7037464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843133</v>
+        <v>127843147</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>91448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444477</v>
+        <v>444554</v>
       </c>
       <c r="R26" t="n">
-        <v>7037464</v>
+        <v>7037482</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,11 +3149,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127843115</v>
+        <v>127843153</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444541</v>
+        <v>444466</v>
       </c>
       <c r="R27" t="n">
-        <v>7037575</v>
+        <v>7037481</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3246,11 +3246,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3277,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843153</v>
+        <v>127843115</v>
       </c>
       <c r="B28" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3312,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444466</v>
+        <v>444541</v>
       </c>
       <c r="R28" t="n">
-        <v>7037481</v>
+        <v>7037575</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3348,6 +3343,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,7 +3377,7 @@
         <v>127843120</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>127843107</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B31" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R31" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,10 +3680,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3691,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R32" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,11 +3751,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843148</v>
+        <v>127843144</v>
       </c>
       <c r="B33" t="n">
-        <v>91378</v>
+        <v>57845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,34 +3788,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444520</v>
+        <v>444731</v>
       </c>
       <c r="R33" t="n">
-        <v>7037511</v>
+        <v>7037835</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3874,10 +3882,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,21 +3893,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3917,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R34" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,11 +3953,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3976,10 +3979,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843144</v>
+        <v>127843108</v>
       </c>
       <c r="B35" t="n">
-        <v>57833</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,42 +3990,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444731</v>
+        <v>444547</v>
       </c>
       <c r="R35" t="n">
-        <v>7037835</v>
+        <v>7037683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4050,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4084,7 +4084,7 @@
         <v>127843106</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>127843103</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127843124</v>
+        <v>127843151</v>
       </c>
       <c r="B38" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444477</v>
+        <v>444480</v>
       </c>
       <c r="R38" t="n">
-        <v>7037536</v>
+        <v>7037529</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4364,11 +4364,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4395,10 +4390,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127843151</v>
+        <v>127843124</v>
       </c>
       <c r="B39" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4406,21 +4401,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4430,10 +4425,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444480</v>
+        <v>444477</v>
       </c>
       <c r="R39" t="n">
-        <v>7037529</v>
+        <v>7037536</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,6 +4461,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4495,7 +4495,7 @@
         <v>127843101</v>
       </c>
       <c r="B40" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>127843139</v>
       </c>
       <c r="B41" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>127843104</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>127843142</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127843138</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>127843111</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>127843105</v>
       </c>
       <c r="B46" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>127843143</v>
       </c>
       <c r="B47" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>127843113</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>127843112</v>
       </c>
       <c r="B49" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843149</v>
+        <v>127843141</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444505</v>
+        <v>444571</v>
       </c>
       <c r="R7" t="n">
-        <v>7037527</v>
+        <v>7037448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843102</v>
+        <v>127843145</v>
       </c>
       <c r="B8" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444566</v>
+        <v>444478</v>
       </c>
       <c r="R8" t="n">
-        <v>7037573</v>
+        <v>7037536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843141</v>
+        <v>127843102</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444571</v>
+        <v>444566</v>
       </c>
       <c r="R9" t="n">
-        <v>7037448</v>
+        <v>7037573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843145</v>
+        <v>127843149</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444478</v>
+        <v>444505</v>
       </c>
       <c r="R10" t="n">
-        <v>7037536</v>
+        <v>7037527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1874,7 +1874,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843126</v>
+        <v>127843110</v>
       </c>
       <c r="B14" t="n">
         <v>57685</v>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444461</v>
+        <v>444513</v>
       </c>
       <c r="R14" t="n">
-        <v>7037529</v>
+        <v>7037512</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843110</v>
+        <v>127843122</v>
       </c>
       <c r="B15" t="n">
         <v>57685</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444513</v>
+        <v>444462</v>
       </c>
       <c r="R15" t="n">
-        <v>7037512</v>
+        <v>7037557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843122</v>
+        <v>127843126</v>
       </c>
       <c r="B16" t="n">
         <v>57685</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444462</v>
+        <v>444461</v>
       </c>
       <c r="R16" t="n">
-        <v>7037557</v>
+        <v>7037529</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B17" t="n">
-        <v>91470</v>
+        <v>91448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R17" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B18" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R18" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843154</v>
+        <v>127843099</v>
       </c>
       <c r="B21" t="n">
-        <v>91470</v>
+        <v>91452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444480</v>
+        <v>444641</v>
       </c>
       <c r="R21" t="n">
-        <v>7037475</v>
+        <v>7037742</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127843099</v>
+        <v>127843154</v>
       </c>
       <c r="B22" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444641</v>
+        <v>444480</v>
       </c>
       <c r="R22" t="n">
-        <v>7037742</v>
+        <v>7037475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843129</v>
+        <v>127843133</v>
       </c>
       <c r="B24" t="n">
         <v>57685</v>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444461</v>
+        <v>444477</v>
       </c>
       <c r="R24" t="n">
-        <v>7037489</v>
+        <v>7037464</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843133</v>
+        <v>127843147</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444477</v>
+        <v>444554</v>
       </c>
       <c r="R25" t="n">
-        <v>7037464</v>
+        <v>7037482</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3047,11 +3047,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843147</v>
+        <v>127843129</v>
       </c>
       <c r="B26" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444554</v>
+        <v>444461</v>
       </c>
       <c r="R26" t="n">
-        <v>7037482</v>
+        <v>7037489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843128</v>
+        <v>127843155</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444473</v>
+        <v>444538</v>
       </c>
       <c r="R31" t="n">
-        <v>7037520</v>
+        <v>7037421</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843155</v>
+        <v>127843128</v>
       </c>
       <c r="B32" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444538</v>
+        <v>444473</v>
       </c>
       <c r="R32" t="n">
-        <v>7037421</v>
+        <v>7037520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,6 +3746,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843144</v>
+        <v>127843148</v>
       </c>
       <c r="B33" t="n">
-        <v>57845</v>
+        <v>91470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,42 +3788,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444731</v>
+        <v>444520</v>
       </c>
       <c r="R33" t="n">
-        <v>7037835</v>
+        <v>7037511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3882,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843148</v>
+        <v>127843108</v>
       </c>
       <c r="B34" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3893,21 +3885,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3917,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444520</v>
+        <v>444547</v>
       </c>
       <c r="R34" t="n">
-        <v>7037511</v>
+        <v>7037683</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,6 +3945,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3979,10 +3976,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843108</v>
+        <v>127843144</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57845</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,34 +3987,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444547</v>
+        <v>444731</v>
       </c>
       <c r="R35" t="n">
-        <v>7037683</v>
+        <v>7037835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4691,7 +4691,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127843104</v>
+        <v>127843142</v>
       </c>
       <c r="B42" t="n">
         <v>57685</v>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444764</v>
+        <v>444554</v>
       </c>
       <c r="R42" t="n">
-        <v>7037903</v>
+        <v>7037489</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4793,7 +4793,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127843142</v>
+        <v>127843104</v>
       </c>
       <c r="B43" t="n">
         <v>57685</v>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444554</v>
+        <v>444764</v>
       </c>
       <c r="R43" t="n">
-        <v>7037489</v>
+        <v>7037903</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5099,7 +5099,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127843105</v>
+        <v>127843143</v>
       </c>
       <c r="B46" t="n">
         <v>57685</v>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444698</v>
+        <v>444720</v>
       </c>
       <c r="R46" t="n">
-        <v>7037783</v>
+        <v>7037681</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,7 +5201,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127843143</v>
+        <v>127843105</v>
       </c>
       <c r="B47" t="n">
         <v>57685</v>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444720</v>
+        <v>444698</v>
       </c>
       <c r="R47" t="n">
-        <v>7037681</v>
+        <v>7037783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -1175,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843141</v>
+        <v>127843145</v>
       </c>
       <c r="B7" t="n">
         <v>57685</v>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444571</v>
+        <v>444478</v>
       </c>
       <c r="R7" t="n">
-        <v>7037448</v>
+        <v>7037536</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843145</v>
+        <v>127843141</v>
       </c>
       <c r="B8" t="n">
         <v>57685</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444478</v>
+        <v>444571</v>
       </c>
       <c r="R8" t="n">
-        <v>7037536</v>
+        <v>7037448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påbörjat bohål?</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,32 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843102</v>
+        <v>127843149</v>
       </c>
       <c r="B9" t="n">
-        <v>92149</v>
+        <v>91470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444566</v>
+        <v>444505</v>
       </c>
       <c r="R9" t="n">
-        <v>7037573</v>
+        <v>7037527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,32 +1476,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843149</v>
+        <v>127843102</v>
       </c>
       <c r="B10" t="n">
-        <v>91470</v>
+        <v>92149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444505</v>
+        <v>444566</v>
       </c>
       <c r="R10" t="n">
-        <v>7037527</v>
+        <v>7037573</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843110</v>
+        <v>127843126</v>
       </c>
       <c r="B14" t="n">
         <v>57685</v>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444513</v>
+        <v>444461</v>
       </c>
       <c r="R14" t="n">
-        <v>7037512</v>
+        <v>7037529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843126</v>
+        <v>127843110</v>
       </c>
       <c r="B16" t="n">
         <v>57685</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444461</v>
+        <v>444513</v>
       </c>
       <c r="R16" t="n">
-        <v>7037529</v>
+        <v>7037512</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843146</v>
+        <v>127843157</v>
       </c>
       <c r="B17" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444502</v>
+        <v>444826</v>
       </c>
       <c r="R17" t="n">
-        <v>7037488</v>
+        <v>7037952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843157</v>
+        <v>127843146</v>
       </c>
       <c r="B18" t="n">
-        <v>91470</v>
+        <v>91448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444826</v>
+        <v>444502</v>
       </c>
       <c r="R18" t="n">
-        <v>7037952</v>
+        <v>7037488</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843099</v>
+        <v>127843154</v>
       </c>
       <c r="B21" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444641</v>
+        <v>444480</v>
       </c>
       <c r="R21" t="n">
-        <v>7037742</v>
+        <v>7037475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127843154</v>
+        <v>127843099</v>
       </c>
       <c r="B22" t="n">
-        <v>91470</v>
+        <v>91452</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444480</v>
+        <v>444641</v>
       </c>
       <c r="R22" t="n">
-        <v>7037475</v>
+        <v>7037742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843133</v>
+        <v>127843147</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444477</v>
+        <v>444554</v>
       </c>
       <c r="R24" t="n">
-        <v>7037464</v>
+        <v>7037482</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2945,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843147</v>
+        <v>127843133</v>
       </c>
       <c r="B25" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2982,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444554</v>
+        <v>444477</v>
       </c>
       <c r="R25" t="n">
-        <v>7037482</v>
+        <v>7037464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3047,6 +3042,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843148</v>
+        <v>127843144</v>
       </c>
       <c r="B33" t="n">
-        <v>91470</v>
+        <v>57845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,34 +3788,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444520</v>
+        <v>444731</v>
       </c>
       <c r="R33" t="n">
-        <v>7037511</v>
+        <v>7037835</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3874,10 +3882,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,21 +3893,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3917,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R34" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,11 +3953,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3976,10 +3979,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843144</v>
+        <v>127843108</v>
       </c>
       <c r="B35" t="n">
-        <v>57845</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,42 +3990,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444731</v>
+        <v>444547</v>
       </c>
       <c r="R35" t="n">
-        <v>7037835</v>
+        <v>7037683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4050,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4081,7 +4081,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843106</v>
+        <v>127843103</v>
       </c>
       <c r="B36" t="n">
         <v>57685</v>
@@ -4110,16 +4110,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444593</v>
+        <v>444547</v>
       </c>
       <c r="R36" t="n">
-        <v>7037659</v>
+        <v>7037649</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4156,7 +4164,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,7 +4191,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127843103</v>
+        <v>127843106</v>
       </c>
       <c r="B37" t="n">
         <v>57685</v>
@@ -4212,24 +4220,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444547</v>
+        <v>444593</v>
       </c>
       <c r="R37" t="n">
-        <v>7037649</v>
+        <v>7037659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4492,32 +4492,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843101</v>
+        <v>127843139</v>
       </c>
       <c r="B40" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444760</v>
+        <v>444511</v>
       </c>
       <c r="R40" t="n">
-        <v>7037894</v>
+        <v>7037473</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4563,6 +4563,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4589,32 +4594,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843139</v>
+        <v>127843101</v>
       </c>
       <c r="B41" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4624,10 +4629,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444511</v>
+        <v>444760</v>
       </c>
       <c r="R41" t="n">
-        <v>7037473</v>
+        <v>7037894</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,11 +4665,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4691,7 +4691,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127843142</v>
+        <v>127843104</v>
       </c>
       <c r="B42" t="n">
         <v>57685</v>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444554</v>
+        <v>444764</v>
       </c>
       <c r="R42" t="n">
-        <v>7037489</v>
+        <v>7037903</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4793,7 +4793,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127843104</v>
+        <v>127843142</v>
       </c>
       <c r="B43" t="n">
         <v>57685</v>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444764</v>
+        <v>444554</v>
       </c>
       <c r="R43" t="n">
-        <v>7037903</v>
+        <v>7037489</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127843138</v>
+        <v>127843111</v>
       </c>
       <c r="B44" t="n">
         <v>57685</v>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444523</v>
+        <v>444514</v>
       </c>
       <c r="R44" t="n">
-        <v>7037462</v>
+        <v>7037529</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4997,7 +4997,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127843111</v>
+        <v>127843138</v>
       </c>
       <c r="B45" t="n">
         <v>57685</v>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444514</v>
+        <v>444523</v>
       </c>
       <c r="R45" t="n">
-        <v>7037529</v>
+        <v>7037462</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5099,7 +5099,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127843143</v>
+        <v>127843105</v>
       </c>
       <c r="B46" t="n">
         <v>57685</v>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444720</v>
+        <v>444698</v>
       </c>
       <c r="R46" t="n">
-        <v>7037681</v>
+        <v>7037783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,7 +5201,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127843105</v>
+        <v>127843143</v>
       </c>
       <c r="B47" t="n">
         <v>57685</v>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444698</v>
+        <v>444720</v>
       </c>
       <c r="R47" t="n">
-        <v>7037783</v>
+        <v>7037681</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843154</v>
+        <v>127843109</v>
       </c>
       <c r="B21" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444480</v>
+        <v>444542</v>
       </c>
       <c r="R21" t="n">
-        <v>7037475</v>
+        <v>7037666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2649,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843109</v>
+        <v>127843154</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2788,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444542</v>
+        <v>444480</v>
       </c>
       <c r="R23" t="n">
-        <v>7037666</v>
+        <v>7037475</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3777,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843144</v>
+        <v>127843108</v>
       </c>
       <c r="B33" t="n">
-        <v>57845</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,42 +3788,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444731</v>
+        <v>444547</v>
       </c>
       <c r="R33" t="n">
-        <v>7037835</v>
+        <v>7037683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3856,6 +3848,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3882,10 +3879,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843148</v>
+        <v>127843144</v>
       </c>
       <c r="B34" t="n">
-        <v>91470</v>
+        <v>57845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3893,34 +3890,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444520</v>
+        <v>444731</v>
       </c>
       <c r="R34" t="n">
-        <v>7037511</v>
+        <v>7037835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3979,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843108</v>
+        <v>127843148</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,21 +3995,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4014,10 +4019,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444547</v>
+        <v>444520</v>
       </c>
       <c r="R35" t="n">
-        <v>7037683</v>
+        <v>7037511</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,11 +4055,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126503198</v>
+        <v>127843146</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällberget vnv, Jmt</t>
+          <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444473</v>
+        <v>444502</v>
       </c>
       <c r="R2" t="n">
-        <v>7037571</v>
+        <v>7037488</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126503200</v>
+        <v>127843147</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällberget vnv, Jmt</t>
+          <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444457</v>
+        <v>444554</v>
       </c>
       <c r="R3" t="n">
-        <v>7037557</v>
+        <v>7037482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126503199</v>
+        <v>126503190</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444471</v>
+        <v>444576</v>
       </c>
       <c r="R4" t="n">
-        <v>7037557</v>
+        <v>7037751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843150</v>
+        <v>127843099</v>
       </c>
       <c r="B5" t="n">
-        <v>91470</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444510</v>
+        <v>444641</v>
       </c>
       <c r="R5" t="n">
-        <v>7037554</v>
+        <v>7037742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843152</v>
+        <v>126503235</v>
       </c>
       <c r="B6" t="n">
-        <v>91470</v>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444458</v>
+        <v>444601</v>
       </c>
       <c r="R6" t="n">
-        <v>7037500</v>
+        <v>7037789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843145</v>
+        <v>127843101</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444478</v>
+        <v>444760</v>
       </c>
       <c r="R7" t="n">
-        <v>7037536</v>
+        <v>7037894</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,16 +1233,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1277,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843141</v>
+        <v>127843102</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444571</v>
+        <v>444566</v>
       </c>
       <c r="R8" t="n">
-        <v>7037448</v>
+        <v>7037573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843149</v>
+        <v>126503234</v>
       </c>
       <c r="B9" t="n">
-        <v>91470</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444505</v>
+        <v>444631</v>
       </c>
       <c r="R9" t="n">
-        <v>7037527</v>
+        <v>7037796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,12 +1419,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,45 +1456,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843102</v>
+        <v>126503191</v>
       </c>
       <c r="B10" t="n">
-        <v>92149</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444566</v>
+        <v>444558</v>
       </c>
       <c r="R10" t="n">
-        <v>7037573</v>
+        <v>7037710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,12 +1521,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127843131</v>
+        <v>126503192</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,14 +1589,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444467</v>
+        <v>444547</v>
       </c>
       <c r="R11" t="n">
-        <v>7037464</v>
+        <v>7037689</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1638,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1675,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127843135</v>
+        <v>126503193</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,14 +1691,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444519</v>
+        <v>444537</v>
       </c>
       <c r="R12" t="n">
-        <v>7037467</v>
+        <v>7037707</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,17 +1725,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843156</v>
+        <v>126503197</v>
       </c>
       <c r="B13" t="n">
-        <v>91470</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,34 +1773,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444572</v>
+        <v>444450</v>
       </c>
       <c r="R13" t="n">
-        <v>7037457</v>
+        <v>7037573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,12 +1827,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843126</v>
+        <v>126503198</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,14 +1895,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444461</v>
+        <v>444473</v>
       </c>
       <c r="R14" t="n">
-        <v>7037529</v>
+        <v>7037571</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,12 +1929,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1976,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843122</v>
+        <v>126503199</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,11 +1997,11 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444462</v>
+        <v>444471</v>
       </c>
       <c r="R15" t="n">
         <v>7037557</v>
@@ -2041,17 +2031,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843110</v>
+        <v>126503200</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,14 +2099,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444513</v>
+        <v>444457</v>
       </c>
       <c r="R16" t="n">
-        <v>7037512</v>
+        <v>7037557</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,17 +2133,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,10 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843157</v>
+        <v>126503201</v>
       </c>
       <c r="B17" t="n">
-        <v>91470</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,34 +2181,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444826</v>
+        <v>444430</v>
       </c>
       <c r="R17" t="n">
-        <v>7037952</v>
+        <v>7037574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,12 +2235,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843146</v>
+        <v>126503233</v>
       </c>
       <c r="B18" t="n">
-        <v>91448</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,34 +2283,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hällberget  V, Jmt</t>
+          <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444502</v>
+        <v>444562</v>
       </c>
       <c r="R18" t="n">
-        <v>7037488</v>
+        <v>7037745</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2342,12 +2337,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127843117</v>
+        <v>127843103</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,16 +2403,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444554</v>
+        <v>444547</v>
       </c>
       <c r="R19" t="n">
-        <v>7037595</v>
+        <v>7037649</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2449,14 +2457,14 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2476,10 +2484,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843140</v>
+        <v>127843104</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,10 +2519,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444560</v>
+        <v>444764</v>
       </c>
       <c r="R20" t="n">
-        <v>7037432</v>
+        <v>7037903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,7 +2559,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2586,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843109</v>
+        <v>127843105</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444542</v>
+        <v>444698</v>
       </c>
       <c r="R21" t="n">
-        <v>7037666</v>
+        <v>7037783</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,7 +2661,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2680,10 +2688,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127843099</v>
+        <v>127843106</v>
       </c>
       <c r="B22" t="n">
-        <v>91452</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,21 +2699,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2723,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444641</v>
+        <v>444593</v>
       </c>
       <c r="R22" t="n">
-        <v>7037742</v>
+        <v>7037659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,6 +2759,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2777,10 +2790,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127843154</v>
+        <v>127843107</v>
       </c>
       <c r="B23" t="n">
-        <v>91470</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2801,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2825,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444480</v>
+        <v>444567</v>
       </c>
       <c r="R23" t="n">
-        <v>7037475</v>
+        <v>7037695</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2861,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2892,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127843147</v>
+        <v>127843108</v>
       </c>
       <c r="B24" t="n">
-        <v>91448</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2903,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2927,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444554</v>
+        <v>444547</v>
       </c>
       <c r="R24" t="n">
-        <v>7037482</v>
+        <v>7037683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,6 +2963,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127843133</v>
+        <v>127843109</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444477</v>
+        <v>444542</v>
       </c>
       <c r="R25" t="n">
-        <v>7037464</v>
+        <v>7037666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3069,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127843129</v>
+        <v>127843110</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,10 +3131,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444461</v>
+        <v>444513</v>
       </c>
       <c r="R26" t="n">
-        <v>7037489</v>
+        <v>7037512</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3148,7 +3171,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3198,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127843153</v>
+        <v>127843111</v>
       </c>
       <c r="B27" t="n">
-        <v>91470</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3209,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3233,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444466</v>
+        <v>444514</v>
       </c>
       <c r="R27" t="n">
-        <v>7037481</v>
+        <v>7037529</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3246,6 +3269,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,10 +3300,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843115</v>
+        <v>127843112</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,10 +3335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444541</v>
+        <v>444532</v>
       </c>
       <c r="R28" t="n">
-        <v>7037575</v>
+        <v>7037525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,7 +3375,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3374,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127843120</v>
+        <v>127843113</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3409,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444461</v>
+        <v>444529</v>
       </c>
       <c r="R29" t="n">
-        <v>7037569</v>
+        <v>7037528</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3476,10 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127843107</v>
+        <v>127843115</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3511,10 +3539,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444567</v>
+        <v>444541</v>
       </c>
       <c r="R30" t="n">
-        <v>7037695</v>
+        <v>7037575</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3578,10 +3606,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127843155</v>
+        <v>127843117</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3617,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3641,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444538</v>
+        <v>444554</v>
       </c>
       <c r="R31" t="n">
-        <v>7037421</v>
+        <v>7037595</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3677,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,10 +3708,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127843128</v>
+        <v>127843120</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3710,10 +3743,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444473</v>
+        <v>444461</v>
       </c>
       <c r="R32" t="n">
-        <v>7037520</v>
+        <v>7037569</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3777,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127843108</v>
+        <v>127843122</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444547</v>
+        <v>444462</v>
       </c>
       <c r="R33" t="n">
-        <v>7037683</v>
+        <v>7037557</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3879,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127843144</v>
+        <v>127843124</v>
       </c>
       <c r="B34" t="n">
-        <v>57845</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3890,42 +3923,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444731</v>
+        <v>444477</v>
       </c>
       <c r="R34" t="n">
-        <v>7037835</v>
+        <v>7037536</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3958,6 +3983,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3984,10 +4014,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843148</v>
+        <v>127843126</v>
       </c>
       <c r="B35" t="n">
-        <v>91470</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,21 +4025,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4019,10 +4049,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444520</v>
+        <v>444461</v>
       </c>
       <c r="R35" t="n">
-        <v>7037511</v>
+        <v>7037529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,6 +4085,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4081,10 +4116,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843103</v>
+        <v>127843128</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4110,24 +4145,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444547</v>
+        <v>444473</v>
       </c>
       <c r="R36" t="n">
-        <v>7037649</v>
+        <v>7037520</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4164,14 +4191,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 3,5 m upp i en död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4191,10 +4218,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127843106</v>
+        <v>127843129</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4226,10 +4253,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444593</v>
+        <v>444461</v>
       </c>
       <c r="R37" t="n">
-        <v>7037659</v>
+        <v>7037489</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,10 +4320,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127843151</v>
+        <v>127843131</v>
       </c>
       <c r="B38" t="n">
-        <v>91470</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,21 +4331,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4328,10 +4355,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444480</v>
+        <v>444467</v>
       </c>
       <c r="R38" t="n">
-        <v>7037529</v>
+        <v>7037464</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4364,6 +4391,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4390,10 +4422,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127843124</v>
+        <v>127843133</v>
       </c>
       <c r="B39" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4428,7 +4460,7 @@
         <v>444477</v>
       </c>
       <c r="R39" t="n">
-        <v>7037536</v>
+        <v>7037464</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4465,7 +4497,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4492,10 +4524,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127843139</v>
+        <v>127843135</v>
       </c>
       <c r="B40" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,10 +4559,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444511</v>
+        <v>444519</v>
       </c>
       <c r="R40" t="n">
-        <v>7037473</v>
+        <v>7037467</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,7 +4599,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4594,32 +4626,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127843101</v>
+        <v>127843138</v>
       </c>
       <c r="B41" t="n">
-        <v>92149</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4629,10 +4661,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444760</v>
+        <v>444523</v>
       </c>
       <c r="R41" t="n">
-        <v>7037894</v>
+        <v>7037462</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4697,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4691,10 +4728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127843104</v>
+        <v>127843139</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,10 +4763,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444764</v>
+        <v>444511</v>
       </c>
       <c r="R42" t="n">
-        <v>7037903</v>
+        <v>7037473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,7 +4803,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4793,10 +4830,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127843142</v>
+        <v>127843140</v>
       </c>
       <c r="B43" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,10 +4865,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444554</v>
+        <v>444560</v>
       </c>
       <c r="R43" t="n">
-        <v>7037489</v>
+        <v>7037432</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4895,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127843111</v>
+        <v>127843141</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4930,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444514</v>
+        <v>444571</v>
       </c>
       <c r="R44" t="n">
-        <v>7037529</v>
+        <v>7037448</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4970,7 +5007,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4997,10 +5034,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127843138</v>
+        <v>127843142</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5032,10 +5069,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444523</v>
+        <v>444554</v>
       </c>
       <c r="R45" t="n">
-        <v>7037462</v>
+        <v>7037489</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5072,7 +5109,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5099,10 +5136,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127843105</v>
+        <v>127843143</v>
       </c>
       <c r="B46" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,10 +5171,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444698</v>
+        <v>444720</v>
       </c>
       <c r="R46" t="n">
-        <v>7037783</v>
+        <v>7037681</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5174,7 +5211,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,10 +5238,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127843143</v>
+        <v>127843145</v>
       </c>
       <c r="B47" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5236,10 +5273,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444720</v>
+        <v>444478</v>
       </c>
       <c r="R47" t="n">
-        <v>7037681</v>
+        <v>7037536</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,14 +5313,14 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -5303,10 +5340,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127843113</v>
+        <v>127843144</v>
       </c>
       <c r="B48" t="n">
-        <v>57685</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5314,34 +5351,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hällberget  V, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444529</v>
+        <v>444731</v>
       </c>
       <c r="R48" t="n">
-        <v>7037528</v>
+        <v>7037835</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5376,11 +5421,6 @@
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5402,108 +5442,6 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>127843112</v>
-      </c>
-      <c r="B49" t="n">
-        <v>57685</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Hällberget  V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>444532</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7037525</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35885-2025 artfynd.xlsx
+++ b/artfynd/A 35885-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843146</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503190</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503235</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843101</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843102</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503234</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503191</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503192</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503193</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503197</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503198</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503199</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503200</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503201</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2371,6 +2456,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126503233</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2481,6 +2571,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843103</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2583,6 +2678,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843104</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2685,6 +2785,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843105</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2787,6 +2892,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843106</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843107</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2991,6 +3106,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843108</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3093,6 +3213,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843109</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3195,6 +3320,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843110</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3297,6 +3427,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843111</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843112</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3501,6 +3641,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843113</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3603,6 +3748,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843115</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3705,6 +3855,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843117</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3807,6 +3962,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843120</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3909,6 +4069,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843122</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4011,6 +4176,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843124</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4113,6 +4283,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843126</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4215,6 +4390,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843128</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4317,6 +4497,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843129</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4419,6 +4604,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843131</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4521,6 +4711,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843133</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4623,6 +4818,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843135</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4725,6 +4925,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843138</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4827,6 +5032,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843139</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4929,6 +5139,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843140</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5031,6 +5246,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843141</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5133,6 +5353,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843142</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5235,6 +5460,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843143</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5337,6 +5567,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843145</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5442,8 +5677,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843144</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>